--- a/py_test_ui/EXCEL FILE/recordCal_PM.xlsx
+++ b/py_test_ui/EXCEL FILE/recordCal_PM.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z615"/>
+  <dimension ref="A1:Z671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66872,6 +66872,6054 @@
       <c r="Y615" t="inlineStr"/>
       <c r="Z615" t="inlineStr"/>
     </row>
+    <row r="616">
+      <c r="A616" t="inlineStr"/>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>33843</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>PYT3_00852</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T616" t="inlineStr"/>
+      <c r="U616" t="inlineStr"/>
+      <c r="V616" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W616" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X616" t="inlineStr"/>
+      <c r="Y616" t="inlineStr"/>
+      <c r="Z616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr"/>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>405069</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>PYT3_09317</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T617" t="inlineStr"/>
+      <c r="U617" t="inlineStr"/>
+      <c r="V617" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W617" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X617" t="inlineStr"/>
+      <c r="Y617" t="inlineStr"/>
+      <c r="Z617" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr"/>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>405070</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>PYT3_09318</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T618" t="inlineStr"/>
+      <c r="U618" t="inlineStr"/>
+      <c r="V618" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W618" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X618" t="inlineStr"/>
+      <c r="Y618" t="inlineStr"/>
+      <c r="Z618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr"/>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>32212</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>PYT3_00303</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T619" t="inlineStr"/>
+      <c r="U619" t="inlineStr"/>
+      <c r="V619" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W619" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X619" t="inlineStr"/>
+      <c r="Y619" t="inlineStr"/>
+      <c r="Z619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr"/>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>32220</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>PYT3_00311</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T620" t="inlineStr"/>
+      <c r="U620" t="inlineStr"/>
+      <c r="V620" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W620" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X620" t="inlineStr"/>
+      <c r="Y620" t="inlineStr"/>
+      <c r="Z620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr"/>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>39095</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>PYT3_02472</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T621" t="inlineStr"/>
+      <c r="U621" t="inlineStr"/>
+      <c r="V621" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W621" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X621" t="inlineStr"/>
+      <c r="Y621" t="inlineStr"/>
+      <c r="Z621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr"/>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>40220</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>PYT3_02627</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T622" t="inlineStr"/>
+      <c r="U622" t="inlineStr"/>
+      <c r="V622" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W622" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X622" t="inlineStr"/>
+      <c r="Y622" t="inlineStr"/>
+      <c r="Z622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr"/>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>110113</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>PYT3_04832</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T623" t="inlineStr"/>
+      <c r="U623" t="inlineStr"/>
+      <c r="V623" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W623" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X623" t="inlineStr"/>
+      <c r="Y623" t="inlineStr"/>
+      <c r="Z623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr"/>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>261025</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>PYT3_07170</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T624" t="inlineStr"/>
+      <c r="U624" t="inlineStr"/>
+      <c r="V624" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W624" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X624" t="inlineStr"/>
+      <c r="Y624" t="inlineStr"/>
+      <c r="Z624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr"/>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>376333</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>PYT3_09010</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T625" t="inlineStr"/>
+      <c r="U625" t="inlineStr"/>
+      <c r="V625" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W625" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X625" t="inlineStr"/>
+      <c r="Y625" t="inlineStr"/>
+      <c r="Z625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr"/>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>252387</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>PYT3_06942</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T626" t="inlineStr"/>
+      <c r="U626" t="inlineStr"/>
+      <c r="V626" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W626" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X626" t="inlineStr"/>
+      <c r="Y626" t="inlineStr"/>
+      <c r="Z626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr"/>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>259344</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>PYT3_07046</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T627" t="inlineStr"/>
+      <c r="U627" t="inlineStr"/>
+      <c r="V627" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W627" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X627" t="inlineStr"/>
+      <c r="Y627" t="inlineStr"/>
+      <c r="Z627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr"/>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>259345</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>PYT3_07047</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q628" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S628" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T628" t="inlineStr"/>
+      <c r="U628" t="inlineStr"/>
+      <c r="V628" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W628" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X628" t="inlineStr"/>
+      <c r="Y628" t="inlineStr"/>
+      <c r="Z628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr"/>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>259347</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>PYT3_07049</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R629" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S629" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T629" t="inlineStr"/>
+      <c r="U629" t="inlineStr"/>
+      <c r="V629" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W629" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X629" t="inlineStr"/>
+      <c r="Y629" t="inlineStr"/>
+      <c r="Z629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr"/>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>260558</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>PYT3_07075</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q630" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R630" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S630" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T630" t="inlineStr"/>
+      <c r="U630" t="inlineStr"/>
+      <c r="V630" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W630" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X630" t="inlineStr"/>
+      <c r="Y630" t="inlineStr"/>
+      <c r="Z630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr"/>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>314152</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>PYT3_08213</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q631" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S631" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T631" t="inlineStr"/>
+      <c r="U631" t="inlineStr"/>
+      <c r="V631" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W631" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X631" t="inlineStr"/>
+      <c r="Y631" t="inlineStr"/>
+      <c r="Z631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr"/>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>408388</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>PYT3_09498</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q632" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R632" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S632" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T632" t="inlineStr"/>
+      <c r="U632" t="inlineStr"/>
+      <c r="V632" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W632" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X632" t="inlineStr"/>
+      <c r="Y632" t="inlineStr"/>
+      <c r="Z632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr"/>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>408389</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>PYT3_09499</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q633" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S633" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T633" t="inlineStr"/>
+      <c r="U633" t="inlineStr"/>
+      <c r="V633" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W633" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X633" t="inlineStr"/>
+      <c r="Y633" t="inlineStr"/>
+      <c r="Z633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr"/>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>411762</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>PYT3_09545</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q634" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S634" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T634" t="inlineStr"/>
+      <c r="U634" t="inlineStr"/>
+      <c r="V634" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W634" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X634" t="inlineStr"/>
+      <c r="Y634" t="inlineStr"/>
+      <c r="Z634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr"/>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>411763</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>PYT3_09546</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q635" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S635" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T635" t="inlineStr"/>
+      <c r="U635" t="inlineStr"/>
+      <c r="V635" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W635" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X635" t="inlineStr"/>
+      <c r="Y635" t="inlineStr"/>
+      <c r="Z635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr"/>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>412772</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>PYT3_09595</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q636" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R636" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S636" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T636" t="inlineStr"/>
+      <c r="U636" t="inlineStr"/>
+      <c r="V636" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W636" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X636" t="inlineStr"/>
+      <c r="Y636" t="inlineStr"/>
+      <c r="Z636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr"/>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>412806</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>PYT3_09596</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q637" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S637" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T637" t="inlineStr"/>
+      <c r="U637" t="inlineStr"/>
+      <c r="V637" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W637" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X637" t="inlineStr"/>
+      <c r="Y637" t="inlineStr"/>
+      <c r="Z637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr"/>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>36490</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>PYT3_01160</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q638" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S638" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T638" t="inlineStr"/>
+      <c r="U638" t="inlineStr"/>
+      <c r="V638" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W638" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X638" t="inlineStr"/>
+      <c r="Y638" t="inlineStr"/>
+      <c r="Z638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr"/>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>33863</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>PYT3_00872</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q639" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R639" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T639" t="inlineStr"/>
+      <c r="U639" t="inlineStr"/>
+      <c r="V639" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W639" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X639" t="inlineStr"/>
+      <c r="Y639" t="inlineStr"/>
+      <c r="Z639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr"/>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>36541</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>PYT3_01211</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q640" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T640" t="inlineStr"/>
+      <c r="U640" t="inlineStr"/>
+      <c r="V640" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W640" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X640" t="inlineStr"/>
+      <c r="Y640" t="inlineStr"/>
+      <c r="Z640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr"/>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>37956</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>PYT3_01730</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q641" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S641" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T641" t="inlineStr"/>
+      <c r="U641" t="inlineStr"/>
+      <c r="V641" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W641" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X641" t="inlineStr"/>
+      <c r="Y641" t="inlineStr"/>
+      <c r="Z641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr"/>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>328195</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>PYT3_08488</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q642" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>Electrical Safety Analyzer</t>
+        </is>
+      </c>
+      <c r="T642" t="inlineStr"/>
+      <c r="U642" t="inlineStr"/>
+      <c r="V642" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W642" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X642" t="inlineStr"/>
+      <c r="Y642" t="inlineStr"/>
+      <c r="Z642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr"/>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>308882</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>PYT3_08117</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q643" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S643" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T643" t="inlineStr"/>
+      <c r="U643" t="inlineStr"/>
+      <c r="V643" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W643" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X643" t="inlineStr"/>
+      <c r="Y643" t="inlineStr"/>
+      <c r="Z643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr"/>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>380475</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>PYT3_09075</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q644" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S644" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T644" t="inlineStr"/>
+      <c r="U644" t="inlineStr"/>
+      <c r="V644" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W644" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X644" t="inlineStr"/>
+      <c r="Y644" t="inlineStr"/>
+      <c r="Z644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr"/>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>398937</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>PYT3_09232</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q645" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S645" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T645" t="inlineStr"/>
+      <c r="U645" t="inlineStr"/>
+      <c r="V645" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W645" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X645" t="inlineStr"/>
+      <c r="Y645" t="inlineStr"/>
+      <c r="Z645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr"/>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>398938</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>PYT3_09233</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q646" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R646" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S646" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T646" t="inlineStr"/>
+      <c r="U646" t="inlineStr"/>
+      <c r="V646" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W646" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X646" t="inlineStr"/>
+      <c r="Y646" t="inlineStr"/>
+      <c r="Z646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr"/>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>40104</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>PYT3_02511</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q647" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S647" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T647" t="inlineStr"/>
+      <c r="U647" t="inlineStr"/>
+      <c r="V647" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W647" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X647" t="inlineStr"/>
+      <c r="Y647" t="inlineStr"/>
+      <c r="Z647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr"/>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>109948</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>PYT3_04668</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q648" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S648" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T648" t="inlineStr"/>
+      <c r="U648" t="inlineStr"/>
+      <c r="V648" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W648" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X648" t="inlineStr"/>
+      <c r="Y648" t="inlineStr"/>
+      <c r="Z648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr"/>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>401704</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>PYT3_09294</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q649" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S649" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T649" t="inlineStr"/>
+      <c r="U649" t="inlineStr"/>
+      <c r="V649" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W649" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X649" t="inlineStr"/>
+      <c r="Y649" t="inlineStr"/>
+      <c r="Z649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr"/>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>397604</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>PYT3_09200</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q650" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S650" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T650" t="inlineStr"/>
+      <c r="U650" t="inlineStr"/>
+      <c r="V650" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W650" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X650" t="inlineStr"/>
+      <c r="Y650" t="inlineStr"/>
+      <c r="Z650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr"/>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>40505</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>PYT3_02902</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q651" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S651" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T651" t="inlineStr"/>
+      <c r="U651" t="inlineStr"/>
+      <c r="V651" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W651" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X651" t="inlineStr"/>
+      <c r="Y651" t="inlineStr"/>
+      <c r="Z651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr"/>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>109998</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>PYT3_04718</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q652" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S652" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T652" t="inlineStr"/>
+      <c r="U652" t="inlineStr"/>
+      <c r="V652" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W652" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X652" t="inlineStr"/>
+      <c r="Y652" t="inlineStr"/>
+      <c r="Z652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr"/>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>109999</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>PYT3_04719</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q653" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R653" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S653" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T653" t="inlineStr"/>
+      <c r="U653" t="inlineStr"/>
+      <c r="V653" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W653" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X653" t="inlineStr"/>
+      <c r="Y653" t="inlineStr"/>
+      <c r="Z653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr"/>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>110000</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>PYT3_04720</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q654" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S654" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T654" t="inlineStr"/>
+      <c r="U654" t="inlineStr"/>
+      <c r="V654" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W654" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X654" t="inlineStr"/>
+      <c r="Y654" t="inlineStr"/>
+      <c r="Z654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr"/>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>110002</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>PYT3_04722</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q655" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S655" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T655" t="inlineStr"/>
+      <c r="U655" t="inlineStr"/>
+      <c r="V655" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W655" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X655" t="inlineStr"/>
+      <c r="Y655" t="inlineStr"/>
+      <c r="Z655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr"/>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>110011</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>PYT3_04731</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q656" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R656" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S656" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T656" t="inlineStr"/>
+      <c r="U656" t="inlineStr"/>
+      <c r="V656" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W656" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X656" t="inlineStr"/>
+      <c r="Y656" t="inlineStr"/>
+      <c r="Z656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr"/>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>425930</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>PYT3_09944</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q657" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R657" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S657" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T657" t="inlineStr"/>
+      <c r="U657" t="inlineStr"/>
+      <c r="V657" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W657" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X657" t="inlineStr"/>
+      <c r="Y657" t="inlineStr"/>
+      <c r="Z657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr"/>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>38816</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>PYT3_02288</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q658" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S658" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T658" t="inlineStr"/>
+      <c r="U658" t="inlineStr"/>
+      <c r="V658" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W658" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X658" t="inlineStr"/>
+      <c r="Y658" t="inlineStr"/>
+      <c r="Z658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr"/>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>38823</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>PYT3_02295</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q659" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R659" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S659" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T659" t="inlineStr"/>
+      <c r="U659" t="inlineStr"/>
+      <c r="V659" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W659" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X659" t="inlineStr"/>
+      <c r="Y659" t="inlineStr"/>
+      <c r="Z659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr"/>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>40138</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>PYT3_02545</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q660" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S660" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T660" t="inlineStr"/>
+      <c r="U660" t="inlineStr"/>
+      <c r="V660" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W660" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X660" t="inlineStr"/>
+      <c r="Y660" t="inlineStr"/>
+      <c r="Z660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr"/>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>375695</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>PYT3_08994</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q661" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S661" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T661" t="inlineStr"/>
+      <c r="U661" t="inlineStr"/>
+      <c r="V661" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W661" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X661" t="inlineStr"/>
+      <c r="Y661" t="inlineStr"/>
+      <c r="Z661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr"/>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>379742</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>PYT3_09064</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q662" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R662" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S662" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T662" t="inlineStr"/>
+      <c r="U662" t="inlineStr"/>
+      <c r="V662" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W662" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X662" t="inlineStr"/>
+      <c r="Y662" t="inlineStr"/>
+      <c r="Z662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr"/>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>425939</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>PYT3_09953</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q663" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S663" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T663" t="inlineStr"/>
+      <c r="U663" t="inlineStr"/>
+      <c r="V663" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W663" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X663" t="inlineStr"/>
+      <c r="Y663" t="inlineStr"/>
+      <c r="Z663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr"/>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>36481</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>PYT3_01151</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q664" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S664" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T664" t="inlineStr"/>
+      <c r="U664" t="inlineStr"/>
+      <c r="V664" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W664" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X664" t="inlineStr"/>
+      <c r="Y664" t="inlineStr"/>
+      <c r="Z664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr"/>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>40143</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>PYT3_02550</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q665" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T665" t="inlineStr"/>
+      <c r="U665" t="inlineStr"/>
+      <c r="V665" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W665" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X665" t="inlineStr"/>
+      <c r="Y665" t="inlineStr"/>
+      <c r="Z665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr"/>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>179410</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>PYT3_05853</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q666" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T666" t="inlineStr"/>
+      <c r="U666" t="inlineStr"/>
+      <c r="V666" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W666" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X666" t="inlineStr"/>
+      <c r="Y666" t="inlineStr"/>
+      <c r="Z666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr"/>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>216627</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>PYT3_06552</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q667" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T667" t="inlineStr"/>
+      <c r="U667" t="inlineStr"/>
+      <c r="V667" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W667" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X667" t="inlineStr"/>
+      <c r="Y667" t="inlineStr"/>
+      <c r="Z667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr"/>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>260617</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>PYT3_07102</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q668" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T668" t="inlineStr"/>
+      <c r="U668" t="inlineStr"/>
+      <c r="V668" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W668" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X668" t="inlineStr"/>
+      <c r="Y668" t="inlineStr"/>
+      <c r="Z668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr"/>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>323433</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>PYT3_08376</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q669" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T669" t="inlineStr"/>
+      <c r="U669" t="inlineStr"/>
+      <c r="V669" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W669" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X669" t="inlineStr"/>
+      <c r="Y669" t="inlineStr"/>
+      <c r="Z669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr"/>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>40170</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>PYT3D_02577</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T670" t="inlineStr"/>
+      <c r="U670" t="inlineStr"/>
+      <c r="V670" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W670" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X670" t="inlineStr"/>
+      <c r="Y670" t="inlineStr"/>
+      <c r="Z670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr"/>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>40177</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>PYT3D_02584</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T671" t="inlineStr"/>
+      <c r="U671" t="inlineStr"/>
+      <c r="V671" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W671" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X671" t="inlineStr"/>
+      <c r="Y671" t="inlineStr"/>
+      <c r="Z671" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/py_test_ui/EXCEL FILE/recordCal_PM.xlsx
+++ b/py_test_ui/EXCEL FILE/recordCal_PM.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,12 +568,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>216598</t>
+          <t>352896</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PYT3_06523</t>
+          <t>LAB-PY3-108</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,22 +603,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -686,11 +686,7 @@
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>PHYATHAI BEAUTY CENTER</t>
-        </is>
-      </c>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -700,12 +696,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>276701</t>
+          <t>353303</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PYT3_07564</t>
+          <t>LAB-PY3-112</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -735,22 +731,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -818,11 +814,2439 @@
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>X-RAY</t>
-        </is>
-      </c>
+      <c r="Z3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>353305</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LAB-PY3-113</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>353306</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LAB-PY3-114</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>353307</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LAB-PY3-115</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>353554</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LAB-PY3-117</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>353555</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LAB-PY3-118</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>353557</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LAB-PY3-120</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>353573</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LAB-PY3-126</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>354754</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LAB-PY3-129</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>354755</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LAB-PY3-130</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>354756</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LAB-PY3-131</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>354786</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LAB-PY3-138</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>400627</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LAB-PY3-152</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>400633</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LAB-PY3-154</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>400634</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LAB-PY3-155</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>406508</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LAB-PY3-159</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>428923</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LAB-PY3-166</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>428924</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LAB-PY3-167</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>428925</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LAB-PY3-168</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>428926</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LAB-PY3-169</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BME</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SOM KONKAEW</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>577199</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>DARANPHOP YIMYAM</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>PM doable</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Perform CAL</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
